--- a/Result/profitability/3680.xlsx
+++ b/Result/profitability/3680.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2.31</v>
+        <v>2.4525</v>
       </c>
       <c r="N2" t="n">
-        <v>43.205</v>
+        <v>42.61875000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>1.72625</v>
+        <v>2.07625</v>
       </c>
       <c r="N3" t="n">
-        <v>43.0425</v>
+        <v>43.805</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.76</v>
+        <v>2.17625</v>
       </c>
       <c r="N4" t="n">
-        <v>44.23875</v>
+        <v>44.23375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>1.64375</v>
+        <v>2.28</v>
       </c>
       <c r="N5" t="n">
-        <v>45.47125</v>
+        <v>45.82625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6675</v>
+        <v>2.16375</v>
       </c>
       <c r="N6" t="n">
-        <v>46.5525</v>
+        <v>47.13375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4725</v>
+        <v>1.51</v>
       </c>
       <c r="N7" t="n">
-        <v>47.15625</v>
+        <v>47.20999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9225</v>
+        <v>1.295</v>
       </c>
       <c r="N8" t="n">
-        <v>47.60875</v>
+        <v>47.74375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9195,6 +9195,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2315</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F70" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="G70" t="n">
+        <v>400</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>17.28%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>289</v>
+      </c>
+      <c r="J70" t="n">
+        <v>689</v>
+      </c>
+      <c r="K70" t="n">
+        <v>532</v>
+      </c>
+      <c r="L70" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.07875</v>
+      </c>
+      <c r="N70" t="n">
+        <v>42.41375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.168627450980392</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1.079999999999998</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.02533427163969026</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>11.56818181818182</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>2.840000000000003</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.06948862246146326</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
